--- a/output/Data and Chart Outputs/north_macedonia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/north_macedonia_power_capacity.xlsx
@@ -873,7 +873,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 07:35 UTC; years 2021-2026</t>
+          <t>2026-10-03 10:55 UTC; years 2021-2026</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/north_macedonia_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/north_macedonia_power_capacity.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>North Macedonia installed generating capacity (ENTSO-E, annual) (to 2026)</a:t>
             </a:r>
           </a:p>
@@ -288,7 +289,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -316,7 +317,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -344,7 +345,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -372,7 +373,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -873,7 +874,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 10:55 UTC; years 2021-2026</t>
+          <t>2026-10-28 01:11 UTC; years 2021-2026</t>
         </is>
       </c>
     </row>
